--- a/Windows_Ransomware_Intrusion/evidence/BrowserArtifacts/Web Downloads 20260424083850.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/BrowserArtifacts/Web Downloads 20260424083850.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\evidence\BrowserArtifacts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/BrowserArtifacts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D43A5D14-88ED-4FF6-9EB4-0C7BF8312AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3185123A-5A96-B846-B46C-08188919C9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8904" yWindow="0" windowWidth="14232" windowHeight="12336" xr2:uid="{34999119-C533-4DFA-941C-5395E0186390}"/>
+    <workbookView xWindow="8900" yWindow="500" windowWidth="19900" windowHeight="17500" xr2:uid="{34999119-C533-4DFA-941C-5395E0186390}"/>
   </bookViews>
   <sheets>
     <sheet name="Web Downloads 20260424083850" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>Source Name</t>
   </si>
@@ -50,63 +50,6 @@
   </si>
   <si>
     <t>Microsoft Edge</t>
-  </si>
-  <si>
-    <t>C:\Users\mtann\Downloads\fema_pda_public-assistance-documentation-checklist.pdf</t>
-  </si>
-  <si>
-    <t>https://www.fema.gov/sites/default/files/documents/fema_pda_public-assistance-documentation-checklist.pdf</t>
-  </si>
-  <si>
-    <t>2026-04-24 12:53:17 EDT</t>
-  </si>
-  <si>
-    <t>fema.gov</t>
-  </si>
-  <si>
-    <t>C:\Users\mtann\Downloads\fema_npd_developing-and-maintaining-emergency_052125.pdf</t>
-  </si>
-  <si>
-    <t>https://www.fema.gov/sites/default/files/documents/fema_npd_developing-and-maintaining-emergency_052125.pdf</t>
-  </si>
-  <si>
-    <t>2026-04-24 12:53:47 EDT</t>
-  </si>
-  <si>
-    <t>C:\Users\mtann\Downloads\NIST.SP.800-12r1.pdf</t>
-  </si>
-  <si>
-    <t>https://nvlpubs.nist.gov/nistpubs/SpecialPublications/NIST.SP.800-12r1.pdf</t>
-  </si>
-  <si>
-    <t>2026-04-24 12:54:36 EDT</t>
-  </si>
-  <si>
-    <t>nist.gov</t>
-  </si>
-  <si>
-    <t>C:\Users\mtann\Downloads\Book.xlsx</t>
-  </si>
-  <si>
-    <t>https://onedrive.live.com/personal/a2400b1b1a26eb7c/_layouts/15/download.aspx?UniqueId=06e2df31%2Dbd8f%2D47d7%2Db679%2D43fc4c067ebf</t>
-  </si>
-  <si>
-    <t>2026-04-24 12:56:01 EDT</t>
-  </si>
-  <si>
-    <t>live.com</t>
-  </si>
-  <si>
-    <t>C:\Users\mtann\Desktop\PBTG-Bridge-Barron-County-WI-e1712253655978.webp</t>
-  </si>
-  <si>
-    <t>https://www.shortspansteelbridges.org/wp-content/uploads/2023/08/PBTG-Bridge-Barron-County-WI-e1712253655978.png</t>
-  </si>
-  <si>
-    <t>2026-04-24 12:57:04 EDT</t>
-  </si>
-  <si>
-    <t>shortspansteelbridges.org</t>
   </si>
   <si>
     <t>C:\Users\mtann\Downloads\bih-chapter9.pdf</t>
@@ -672,6 +615,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82BAD07D-22EE-244A-A43E-57C2281AB6B1}" name="Table1" displayName="Table1" ref="A1:G3" totalsRowShown="0">
+  <autoFilter ref="A1:G3" xr:uid="{82BAD07D-22EE-244A-A43E-57C2281AB6B1}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{6ADD3699-C163-214E-977D-D255DC11281E}" name="Source Name"/>
+    <tableColumn id="2" xr3:uid="{39A6E7D0-3B6B-814A-891B-F908322A5F53}" name="Path"/>
+    <tableColumn id="3" xr3:uid="{12346126-290E-BE47-907F-E72B67B0FC1B}" name="URL"/>
+    <tableColumn id="4" xr3:uid="{587588BA-3B5F-8E45-BD0F-658B02E82141}" name="Date Accessed"/>
+    <tableColumn id="5" xr3:uid="{B352A9FF-63AC-7946-96CD-E24DB30DD09C}" name="Domain"/>
+    <tableColumn id="6" xr3:uid="{CBC8383F-9518-F844-A246-09D6DB4027AB}" name="Username"/>
+    <tableColumn id="7" xr3:uid="{9B09D350-F2AE-AB49-B719-C70499224F45}" name="Program Name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -991,19 +950,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78863D49-176A-4C2F-8D97-7FB84A1CFD15}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="76.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="125.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="67.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="75.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1026,7 +985,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1049,7 +1008,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1063,131 +1022,19 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>